--- a/utils/monday_sprint_sprint_2023-14.xlsx
+++ b/utils/monday_sprint_sprint_2023-14.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="181">
   <si>
     <t>Ticket</t>
   </si>
@@ -132,7 +132,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Semana 4</t>
@@ -4196,7 +4196,7 @@
         <v>21</v>
       </c>
       <c r="Q12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -4219,13 +4219,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="Q13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
         <v>29</v>
       </c>
@@ -4237,12 +4237,6 @@
       </c>
       <c r="N14">
         <v>0</v>
-      </c>
-      <c r="P14" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q14">
-        <v>14</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
@@ -4296,7 +4290,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>33</v>

--- a/utils/monday_sprint_sprint_2023-14.xlsx
+++ b/utils/monday_sprint_sprint_2023-14.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="225">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>3332</t>
+    <t>1407234879</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>20/06/2021</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>10/06/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>16253</t>
+    <t>3808503126</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -114,6 +114,9 @@
     <t>13/01/2023</t>
   </si>
   <si>
+    <t>18/06/2023</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
@@ -138,7 +141,7 @@
     <t>Semana 1</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>4511692477</t>
   </si>
   <si>
     <t>Apontamento Registro de Pintura.</t>
@@ -150,13 +153,16 @@
     <t>22/05/2023</t>
   </si>
   <si>
+    <t>17/06/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
     <t>Maio</t>
   </si>
   <si>
-    <t>18941</t>
+    <t>4581873153</t>
   </si>
   <si>
     <t>Produtivo em horas</t>
@@ -165,82 +171,94 @@
     <t>02/06/2023</t>
   </si>
   <si>
-    <t>20409</t>
+    <t>4580917027</t>
   </si>
   <si>
     <t>Informações de Estorno</t>
   </si>
   <si>
-    <t>20404</t>
+    <t>4580938827</t>
   </si>
   <si>
     <t>Gerar informações de peças estornadas</t>
   </si>
   <si>
-    <t>20131</t>
+    <t>4580964436</t>
   </si>
   <si>
     <t>Informações de Desmoldagem e outras informações sobre o CPP</t>
   </si>
   <si>
-    <t>20110</t>
+    <t>4580991096</t>
   </si>
   <si>
     <t>Relatório Lead Time</t>
   </si>
   <si>
-    <t>19967</t>
+    <t>4581046070</t>
   </si>
   <si>
     <t>Verificação - Planilha de Peso Agrupado</t>
   </si>
   <si>
-    <t>19008</t>
+    <t>12/06/2023</t>
+  </si>
+  <si>
+    <t>4581057752</t>
   </si>
   <si>
     <t>Exceção para o cliente Cryostar</t>
   </si>
   <si>
-    <t>19027</t>
+    <t>4581075827</t>
   </si>
   <si>
     <t>Incluir coluna Planilha do MPS</t>
   </si>
   <si>
-    <t>14310</t>
+    <t>4592188271</t>
   </si>
   <si>
     <t>Sistema de  criação  de  retrabalho - abrir pendencia no fluxo - PARTE 1</t>
   </si>
   <si>
-    <t>20466</t>
+    <t>4581385552</t>
   </si>
   <si>
     <t>Inclusão de colunas - Gestão de Estoque</t>
   </si>
   <si>
-    <t>20508</t>
+    <t>4581457301</t>
   </si>
   <si>
     <t>Criar relatório de roteiros de produção para análise de erros de roteiro</t>
   </si>
   <si>
+    <t>4672812957</t>
+  </si>
+  <si>
     <t>Alteração das rotinas de cálculo de data prevista e MPS.</t>
   </si>
   <si>
     <t>20/06/2023</t>
   </si>
   <si>
+    <t>12/07/2023</t>
+  </si>
+  <si>
     <t>4745933936</t>
   </si>
   <si>
     <t>03/07/2023</t>
   </si>
   <si>
+    <t>16/07/2023</t>
+  </si>
+  <si>
     <t>Julho</t>
   </si>
   <si>
-    <t>19253</t>
+    <t>4735293242</t>
   </si>
   <si>
     <t>Identificação do MPS na carteira</t>
@@ -249,10 +267,13 @@
     <t>30/06/2023</t>
   </si>
   <si>
+    <t>09/07/2023</t>
+  </si>
+  <si>
     <t>Semana 5</t>
   </si>
   <si>
-    <t>19406</t>
+    <t>4735326943</t>
   </si>
   <si>
     <t>Projeto FATURA - Incluir data de liberação calculada no planilha do ERP</t>
@@ -261,25 +282,31 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>19408</t>
+    <t>05/07/2023</t>
+  </si>
+  <si>
+    <t>4735353107</t>
   </si>
   <si>
     <t>Projeto FATURA - Utilizar planilha de cenários como base para o planilha do MPS (baixa prioridade).</t>
   </si>
   <si>
-    <t>19410</t>
+    <t>4735365560</t>
   </si>
   <si>
     <t>Projeto FATURA - Correção de Agrupamento de Etapas USE</t>
   </si>
   <si>
-    <t>19954</t>
+    <t>13/07/2023</t>
+  </si>
+  <si>
+    <t>4735380976</t>
   </si>
   <si>
     <t>Planilha MPS</t>
   </si>
   <si>
-    <t>21220</t>
+    <t>4813043392</t>
   </si>
   <si>
     <t>Projeto FATURA - Gerar um planilhão com base nos cenários 4 e 5 durante o fim de semana de 15/07/23</t>
@@ -288,28 +315,37 @@
     <t>14/07/2023</t>
   </si>
   <si>
+    <t>17/07/2023</t>
+  </si>
+  <si>
     <t>4927461583</t>
   </si>
   <si>
     <t>03/08/2023</t>
   </si>
   <si>
+    <t>07/08/2023</t>
+  </si>
+  <si>
     <t>Agosto</t>
   </si>
   <si>
-    <t>19181</t>
+    <t>4590890149</t>
   </si>
   <si>
     <t>Novo processo de OTFs de Serviços/Ferramentais - Ciclo de Testes</t>
   </si>
   <si>
-    <t>20488</t>
+    <t>15/06/2023</t>
+  </si>
+  <si>
+    <t>4581406566</t>
   </si>
   <si>
     <t>Tela de Desmoldagem - Observação</t>
   </si>
   <si>
-    <t>20339</t>
+    <t>4588433870</t>
   </si>
   <si>
     <t>Verificar Campo de Observação das Invoices de Pagamento</t>
@@ -318,61 +354,76 @@
     <t>4592918979</t>
   </si>
   <si>
-    <t>18614</t>
+    <t>4591761116</t>
   </si>
   <si>
     <t>Alteração apontamento de solda</t>
   </si>
   <si>
-    <t>20359</t>
+    <t>4581348611</t>
   </si>
   <si>
     <t>Replicar o registro para o setor “preparação”</t>
   </si>
   <si>
-    <t>20593</t>
+    <t>11/06/2023</t>
+  </si>
+  <si>
+    <t>4581611237</t>
   </si>
   <si>
     <t>Alteração de registro USE/ULE</t>
   </si>
   <si>
-    <t>19378</t>
+    <t>4652561741</t>
   </si>
   <si>
     <t>Reengenharia dos sistemas de expedição - terceira onda</t>
   </si>
   <si>
-    <t>15/06/2023</t>
+    <t>04/07/2023</t>
   </si>
   <si>
     <t>4745934001</t>
   </si>
   <si>
+    <t>4756963706</t>
+  </si>
+  <si>
     <t>Testar integração com nota / conferencia de pré-embarque</t>
   </si>
   <si>
-    <t>05/07/2023</t>
+    <t>4756973669</t>
   </si>
   <si>
     <t>Fazer o inventário geral, por cliente e por modelo</t>
   </si>
   <si>
-    <t>20910</t>
+    <t>15/07/2023</t>
+  </si>
+  <si>
+    <t>4735165758</t>
   </si>
   <si>
     <t>Melhoria sistema de Gráficos de ToTo</t>
   </si>
   <si>
+    <t>4756941977</t>
+  </si>
+  <si>
     <t>Personalizar o layout de (3 modelos de etiquetas Ticket de embarque, Romaneio e Etiqueta padrao Altona)</t>
   </si>
   <si>
+    <t>4666219232</t>
+  </si>
+  <si>
     <t>Reengenharia sistema expedição - Quarta onda</t>
   </si>
   <si>
     <t>19/06/2023</t>
   </si>
   <si>
-    <t>20087</t>
+    <t>4425837925</t>
   </si>
   <si>
     <t>Segunda Onda - Sistema de Logística Interna</t>
@@ -384,12 +435,15 @@
     <t>4927461673</t>
   </si>
   <si>
-    <t>19908</t>
+    <t>4426303474</t>
   </si>
   <si>
     <t>Desenvolvimento de site web para espelhando do SMI em mobile</t>
   </si>
   <si>
+    <t>4472039895</t>
+  </si>
+  <si>
     <t>Tarefas Preventivas (acesso a flegar as execuções realizadas, descrever os trabalhos realizados e confirmar o serviço)</t>
   </si>
   <si>
@@ -399,37 +453,40 @@
     <t>4592919060</t>
   </si>
   <si>
-    <t>20632</t>
+    <t>4591484144</t>
   </si>
   <si>
     <t>Melhorias Sistema de Manutenção - SS</t>
   </si>
   <si>
-    <t>20605</t>
+    <t>4591530412</t>
   </si>
   <si>
     <t>Bloqueio Requisições MP Centros de Custos</t>
   </si>
   <si>
-    <t>19738</t>
+    <t>4581149850</t>
   </si>
   <si>
     <t>ETF - Criar botão</t>
   </si>
   <si>
-    <t>20527</t>
+    <t>08/06/2023</t>
+  </si>
+  <si>
+    <t>4581500188</t>
   </si>
   <si>
     <t>Geração de Excel em relatório de MTBF - MTTR - DISPONIBILIDADE (TABELA DE HORAS)</t>
   </si>
   <si>
-    <t>19721</t>
+    <t>4581169313</t>
   </si>
   <si>
     <t>Relatório de Peças em Estoque de Terceiros</t>
   </si>
   <si>
-    <t>20661</t>
+    <t>4597040663</t>
   </si>
   <si>
     <t>Bloqueio SIC x Orçamento</t>
@@ -438,7 +495,7 @@
     <t>06/06/2023</t>
   </si>
   <si>
-    <t>20663</t>
+    <t>4597059348</t>
   </si>
   <si>
     <t>Informação SIC</t>
@@ -447,64 +504,79 @@
     <t>4745934065</t>
   </si>
   <si>
-    <t>20980</t>
+    <t>4734964792</t>
   </si>
   <si>
     <t>Configuração Alçadas</t>
   </si>
   <si>
-    <t>20899</t>
+    <t>4735211061</t>
   </si>
   <si>
     <t>Mudança no layout na tela de Baixar OS Preventivas</t>
   </si>
   <si>
-    <t>20995</t>
+    <t>4734935264</t>
   </si>
   <si>
     <t>Data de CPC Prevista Planilha Forecast</t>
   </si>
   <si>
-    <t>20990</t>
+    <t>4734951349</t>
   </si>
   <si>
     <t>Remessa Terceiros - Identificação Sequências Obs NF</t>
   </si>
   <si>
-    <t>20973</t>
+    <t>4735094440</t>
   </si>
   <si>
     <t>Campos Faturamento</t>
   </si>
   <si>
-    <t>20857</t>
+    <t>4735275241</t>
   </si>
   <si>
     <t>Teste Inserto - Modelo EAA11604TESTEINSERTO - OTF 156746</t>
   </si>
   <si>
-    <t>6609</t>
+    <t>06/07/2023</t>
+  </si>
+  <si>
+    <t>4750224515</t>
   </si>
   <si>
     <t>Criar funcionalidade para cadastro da política de estoques em dias corridos no cliente</t>
   </si>
   <si>
-    <t>04/07/2023</t>
+    <t>4750228196</t>
   </si>
   <si>
     <t>Criar indicador no cadastro de cliente de controle de período firme</t>
   </si>
   <si>
+    <t>4750235440</t>
+  </si>
+  <si>
     <t>Carregar tabela de controle de movimentação na carteira</t>
   </si>
   <si>
+    <t>11/07/2023</t>
+  </si>
+  <si>
+    <t>4750258774</t>
+  </si>
+  <si>
     <t>Criar funcionalidade para o envio de e-mail de alerta</t>
   </si>
   <si>
+    <t>4734901032</t>
+  </si>
+  <si>
     <t>Controle de Alterações na carteira dentro do período firme</t>
   </si>
   <si>
-    <t>19833</t>
+    <t>4581107238</t>
   </si>
   <si>
     <t>Liberar acesso - CPP/manutenção/manutenção/roteiro de produção/atividades complementares</t>
@@ -519,7 +591,7 @@
     <t>[ANÁLISE] Rastreabilidade de Terceiros SPS - Retorno e movimentação</t>
   </si>
   <si>
-    <t>20884</t>
+    <t>4735231869</t>
   </si>
   <si>
     <t>Controle do tipo de embalagem</t>
@@ -534,7 +606,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-14</t>
+    <t>Jun/2021</t>
   </si>
   <si>
     <t>Base</t>
@@ -1176,7 +1248,7 @@
         <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1185,33 +1257,33 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>21</v>
@@ -1220,10 +1292,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1232,7 +1304,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1240,7 +1312,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1252,13 +1324,13 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>21</v>
@@ -1267,10 +1339,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1279,15 +1351,15 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1299,13 +1371,13 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>21</v>
@@ -1314,10 +1386,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1326,7 +1398,7 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1334,7 +1406,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1346,25 +1418,25 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1373,7 +1445,7 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1381,7 +1453,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1393,13 +1465,13 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>21</v>
@@ -1408,10 +1480,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1420,7 +1492,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1428,7 +1500,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1440,13 +1512,13 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>21</v>
@@ -1455,10 +1527,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1467,7 +1539,7 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -1475,7 +1547,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1487,13 +1559,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>21</v>
@@ -1502,7 +1574,7 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>24</v>
@@ -1514,7 +1586,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -1522,7 +1594,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1534,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>21</v>
@@ -1549,10 +1621,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1561,7 +1633,7 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -1569,7 +1641,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1581,13 +1653,13 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>21</v>
@@ -1596,10 +1668,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1608,7 +1680,7 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -1616,7 +1688,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1628,13 +1700,13 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>21</v>
@@ -1643,10 +1715,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1655,7 +1727,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>28</v>
@@ -1663,7 +1735,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1675,13 +1747,13 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>21</v>
@@ -1690,10 +1762,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1702,7 +1774,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1710,7 +1782,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1722,13 +1794,13 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>21</v>
@@ -1737,10 +1809,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1749,7 +1821,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1757,7 +1829,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1769,13 +1841,13 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>21</v>
@@ -1784,10 +1856,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1796,7 +1868,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1804,7 +1876,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1816,13 +1888,13 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>21</v>
@@ -1831,10 +1903,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1851,25 +1923,25 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>21</v>
@@ -1878,10 +1950,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1890,15 +1962,15 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1910,13 +1982,13 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>21</v>
@@ -1925,10 +1997,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1937,7 +2009,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -1945,7 +2017,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1957,13 +2029,13 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>21</v>
@@ -1972,10 +2044,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1984,7 +2056,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -1992,7 +2064,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2004,25 +2076,25 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -2031,7 +2103,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -2039,7 +2111,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2051,34 +2123,34 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -2086,7 +2158,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2098,13 +2170,13 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>21</v>
@@ -2113,10 +2185,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2125,7 +2197,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -2133,7 +2205,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2145,13 +2217,13 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
@@ -2160,10 +2232,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2172,33 +2244,33 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>21</v>
@@ -2207,10 +2279,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2219,15 +2291,15 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2239,13 +2311,13 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>21</v>
@@ -2254,10 +2326,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2266,7 +2338,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2274,7 +2346,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2286,13 +2358,13 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>21</v>
@@ -2301,10 +2373,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2313,7 +2385,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -2321,7 +2393,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2333,13 +2405,13 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>21</v>
@@ -2348,10 +2420,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2360,7 +2432,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>28</v>
@@ -2368,25 +2440,25 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>21</v>
@@ -2395,10 +2467,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2407,7 +2479,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -2415,7 +2487,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2427,13 +2499,13 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>21</v>
@@ -2442,10 +2514,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2454,7 +2526,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>28</v>
@@ -2462,7 +2534,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2474,13 +2546,13 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>21</v>
@@ -2489,10 +2561,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2501,7 +2573,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2509,7 +2581,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2521,13 +2593,13 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>21</v>
@@ -2536,10 +2608,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2548,7 +2620,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -2556,7 +2628,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2568,13 +2640,13 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>21</v>
@@ -2583,10 +2655,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2603,25 +2675,25 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>21</v>
@@ -2630,10 +2702,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2642,33 +2714,33 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>21</v>
@@ -2677,10 +2749,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2689,33 +2761,33 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>21</v>
@@ -2724,10 +2796,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2736,15 +2808,15 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2756,13 +2828,13 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>21</v>
@@ -2771,10 +2843,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2783,7 +2855,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>28</v>
@@ -2791,25 +2863,25 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>21</v>
@@ -2818,10 +2890,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2830,33 +2902,33 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>21</v>
@@ -2865,10 +2937,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2885,7 +2957,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2897,13 +2969,13 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>21</v>
@@ -2912,10 +2984,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2924,33 +2996,33 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>21</v>
@@ -2959,10 +3031,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2971,15 +3043,15 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2991,13 +3063,13 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>21</v>
@@ -3006,10 +3078,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -3018,15 +3090,15 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3038,13 +3110,13 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>21</v>
@@ -3053,10 +3125,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3068,30 +3140,30 @@
         <v>27</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>21</v>
@@ -3100,10 +3172,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3112,7 +3184,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>28</v>
@@ -3120,7 +3192,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3132,13 +3204,13 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>21</v>
@@ -3147,7 +3219,7 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>24</v>
@@ -3159,7 +3231,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -3167,7 +3239,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3179,13 +3251,13 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>21</v>
@@ -3194,10 +3266,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3206,7 +3278,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>28</v>
@@ -3214,7 +3286,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3226,13 +3298,13 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>21</v>
@@ -3241,10 +3313,10 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3253,7 +3325,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>28</v>
@@ -3261,7 +3333,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3273,13 +3345,13 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>21</v>
@@ -3288,10 +3360,10 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3300,7 +3372,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>28</v>
@@ -3308,7 +3380,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3320,13 +3392,13 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>21</v>
@@ -3335,10 +3407,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3347,7 +3419,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>28</v>
@@ -3355,7 +3427,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3367,13 +3439,13 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>21</v>
@@ -3382,10 +3454,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3394,7 +3466,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>28</v>
@@ -3402,7 +3474,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3414,13 +3486,13 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>21</v>
@@ -3429,10 +3501,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3441,7 +3513,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>28</v>
@@ -3449,25 +3521,25 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>21</v>
@@ -3476,10 +3548,10 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3488,15 +3560,15 @@
         <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3508,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>21</v>
@@ -3523,10 +3595,10 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
@@ -3535,7 +3607,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>28</v>
@@ -3543,7 +3615,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3555,13 +3627,13 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>21</v>
@@ -3570,10 +3642,10 @@
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -3582,7 +3654,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>28</v>
@@ -3590,7 +3662,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3602,13 +3674,13 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>21</v>
@@ -3617,10 +3689,10 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3629,7 +3701,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>28</v>
@@ -3637,7 +3709,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3649,13 +3721,13 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>21</v>
@@ -3664,10 +3736,10 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
@@ -3676,7 +3748,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>28</v>
@@ -3684,7 +3756,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3696,13 +3768,13 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>21</v>
@@ -3711,10 +3783,10 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -3723,7 +3795,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>28</v>
@@ -3731,7 +3803,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3743,13 +3815,13 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>21</v>
@@ -3758,10 +3830,10 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -3770,7 +3842,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>28</v>
@@ -3778,7 +3850,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -3790,13 +3862,13 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>21</v>
@@ -3805,10 +3877,10 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>25</v>
@@ -3817,15 +3889,15 @@
         <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -3837,13 +3909,13 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>21</v>
@@ -3852,10 +3924,10 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>25</v>
@@ -3864,15 +3936,15 @@
         <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
@@ -3884,13 +3956,13 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>21</v>
@@ -3899,10 +3971,10 @@
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>25</v>
@@ -3911,15 +3983,15 @@
         <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -3931,13 +4003,13 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>21</v>
@@ -3946,10 +4018,10 @@
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>25</v>
@@ -3958,15 +4030,15 @@
         <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -3978,13 +4050,13 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>21</v>
@@ -3993,10 +4065,10 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>25</v>
@@ -4005,7 +4077,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>28</v>
@@ -4013,7 +4085,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4025,13 +4097,13 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>21</v>
@@ -4040,10 +4112,10 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>25</v>
@@ -4052,7 +4124,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>28</v>
@@ -4060,25 +4132,25 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>21</v>
@@ -4087,10 +4159,10 @@
         <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>25</v>
@@ -4099,7 +4171,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>28</v>
@@ -4107,7 +4179,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4119,13 +4191,13 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>21</v>
@@ -4134,10 +4206,10 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>25</v>
@@ -4146,7 +4218,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>28</v>
@@ -4154,25 +4226,25 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>21</v>
@@ -4181,10 +4253,10 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>25</v>
@@ -4193,10 +4265,10 @@
         <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4212,23 +4284,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4236,16 +4308,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4256,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>25.42</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -4264,7 +4336,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -4277,7 +4349,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -4285,7 +4357,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4316,12 +4388,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="B2">
         <v>66</v>
@@ -4335,7 +4407,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>25.42</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -4345,25 +4417,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4380,13 +4452,13 @@
         <v>47</v>
       </c>
       <c r="G10" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -4398,21 +4470,21 @@
         <v>66</v>
       </c>
       <c r="P10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q10">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H11">
         <v>11</v>
@@ -4424,16 +4496,16 @@
         <v>66</v>
       </c>
       <c r="M11" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -4444,19 +4516,19 @@
         <v>5</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H12">
         <v>44</v>
       </c>
       <c r="J12" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4465,12 +4537,12 @@
         <v>27</v>
       </c>
       <c r="Q12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4482,41 +4554,29 @@
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H14">
         <v>9</v>
       </c>
       <c r="M14" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
-      <c r="P14" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q14">
-        <v>14</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4524,7 +4584,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4532,7 +4592,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4540,10 +4600,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -4551,7 +4611,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4559,142 +4619,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>194</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>50</v>
+        <v>185</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>743</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>743</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>743</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>743</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
